--- a/data/compra.xlsx
+++ b/data/compra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonzalo\Desktop\repositorios\ejercicios_practicas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E1A19D-7098-422A-8775-18ABE36BE1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B9DE47-AF1C-44C8-8DCE-22AA5A54CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9073588-D359-49DA-86B1-57759252CDCF}"/>
   </bookViews>
@@ -41,10 +41,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>productos_id</t>
+    <t>quantity</t>
   </si>
   <si>
-    <t>quantity</t>
+    <t>product_id</t>
   </si>
 </sst>
 </file>
@@ -109,7 +109,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0F724C02-3AA0-47CA-B47D-41D54E58D220}" name="Tabla1" displayName="Tabla1" ref="A1:B10" totalsRowShown="0">
   <autoFilter ref="A1:B10" xr:uid="{0F724C02-3AA0-47CA-B47D-41D54E58D220}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CE8054EC-2810-4A0F-81F9-459C3F565B52}" name="productos_id"/>
+    <tableColumn id="1" xr3:uid="{CE8054EC-2810-4A0F-81F9-459C3F565B52}" name="product_id"/>
     <tableColumn id="2" xr3:uid="{3723B794-7DA3-4246-AE02-92B46CEF5AAD}" name="quantity"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -438,10 +438,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
